--- a/ZonasEscolares/excels/JUNIN-SATIPO-PANGOA.xlsx
+++ b/ZonasEscolares/excels/JUNIN-SATIPO-PANGOA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/JUNIN-SATIPO-PANGOA.xlsx
+++ b/ZonasEscolares/excels/JUNIN-SATIPO-PANGOA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>241</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-11.4333</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-74.4853</v>
-      </c>
-      <c r="I2" t="n">
-        <v>263</v>
-      </c>
-      <c r="J2" t="n">
-        <v>12</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-11.4333</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-74.4853</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>30636</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-11.4334</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-74.4832</v>
-      </c>
-      <c r="I3" t="n">
-        <v>995</v>
-      </c>
-      <c r="J3" t="n">
-        <v>36</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-11.4334</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-74.4832</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>995</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>30637 ANDRES AVELINO CACERES</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-11.430946</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-74.487804</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1503</v>
-      </c>
-      <c r="J4" t="n">
-        <v>63</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-11.430946</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-74.487804</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>30671</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-11.580691</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-74.407473</v>
-      </c>
-      <c r="I5" t="n">
-        <v>256</v>
-      </c>
-      <c r="J5" t="n">
-        <v>15</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-11.580691</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-74.407473</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>30675</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-11.6467</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-74.3715</v>
-      </c>
-      <c r="I6" t="n">
-        <v>253</v>
-      </c>
-      <c r="J6" t="n">
-        <v>15</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-11.6467</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-74.3715</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>SAN JUAN</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-11.6477</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-74.3689</v>
-      </c>
-      <c r="I7" t="n">
-        <v>285</v>
-      </c>
-      <c r="J7" t="n">
-        <v>15</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-11.6477</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-74.3689</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>COOPERATIVO PANGOA</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-11.435996</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-74.49329400000001</v>
-      </c>
-      <c r="I8" t="n">
-        <v>272</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-11.435996</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-74.493294</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>JORGE CHAVEZ</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-11.4236</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-74.48715</v>
-      </c>
-      <c r="I9" t="n">
-        <v>229</v>
-      </c>
-      <c r="J9" t="n">
-        <v>15</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-11.4236</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-74.48715</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>SAN DANIEL</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-11.437829</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-74.490172</v>
-      </c>
-      <c r="I10" t="n">
-        <v>888</v>
-      </c>
-      <c r="J10" t="n">
-        <v>41</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-11.437829</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-74.490172</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>HORIZONTE - SAC</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-11.43002</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-74.48904</v>
-      </c>
-      <c r="I11" t="n">
-        <v>279</v>
-      </c>
-      <c r="J11" t="n">
-        <v>14</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-11.43002</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-74.48904</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>CIENTIFICA DEL VRAEM</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-11.42922</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-74.49333</v>
-      </c>
-      <c r="I12" t="n">
-        <v>275</v>
-      </c>
-      <c r="J12" t="n">
-        <v>15</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-11.42922</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-74.49333</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>CESAR'S</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-11.43481</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-74.4885</v>
-      </c>
-      <c r="I13" t="n">
-        <v>377</v>
-      </c>
-      <c r="J13" t="n">
-        <v>14</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-11.43481</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-74.4885</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/JUNIN-SATIPO-PANGOA.xlsx
+++ b/ZonasEscolares/excels/JUNIN-SATIPO-PANGOA.xlsx
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>241231</t>
+          <t>722273</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30636</t>
+          <t>HORIZONTE - SAC</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-11.4334</t>
+          <t>-11.43002</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-74.4832</t>
+          <t>-74.48904</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>279</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>241245</t>
+          <t>864494</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30637 ANDRES AVELINO CACERES</t>
+          <t>CESAR'S</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-11.430946</t>
+          <t>-11.43481</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-74.487804</t>
+          <t>-74.4885</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>377</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>242315</t>
+          <t>242320</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>COOPERATIVO PANGOA</t>
+          <t>JORGE CHAVEZ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-11.435996</t>
+          <t>-11.4236</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-74.493294</t>
+          <t>-74.48715</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>229</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,27 +935,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>242320</t>
+          <t>756531</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JORGE CHAVEZ</t>
+          <t>CIENTIFICA DEL VRAEM</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-11.4236</t>
+          <t>-11.42922</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-74.48715</t>
+          <t>-74.49333</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>275</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>652958</t>
+          <t>241231</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SAN DANIEL</t>
+          <t>30636</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-11.437829</t>
+          <t>-11.4334</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-74.490172</t>
+          <t>-74.4832</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>995</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>722273</t>
+          <t>242315</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>HORIZONTE - SAC</t>
+          <t>COOPERATIVO PANGOA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-11.43002</t>
+          <t>-11.435996</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-74.48904</t>
+          <t>-74.493294</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>272</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>756531</t>
+          <t>652958</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CIENTIFICA DEL VRAEM</t>
+          <t>SAN DANIEL</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-11.42922</t>
+          <t>-11.437829</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-74.49333</t>
+          <t>-74.490172</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>888</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>864494</t>
+          <t>241245</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CESAR'S</t>
+          <t>30637 ANDRES AVELINO CACERES</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-11.43481</t>
+          <t>-11.430946</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-74.4885</t>
+          <t>-74.487804</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">

--- a/ZonasEscolares/excels/JUNIN-SATIPO-PANGOA.xlsx
+++ b/ZonasEscolares/excels/JUNIN-SATIPO-PANGOA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>241085</t>
+          <t>864494</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>CESAR'S</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-11.4333</t>
+          <t>377</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-74.4853</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>-11.43481</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-74.4885</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>722273</t>
+          <t>756531</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>HORIZONTE - SAC</t>
+          <t>CIENTIFICA DEL VRAEM</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-11.43002</t>
+          <t>275</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-74.48904</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>-11.42922</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-74.49333</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>864494</t>
+          <t>722273</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CESAR'S</t>
+          <t>HORIZONTE - SAC</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-11.43481</t>
+          <t>279</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-74.4885</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>-11.43002</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-74.48904</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>241269</t>
+          <t>652958</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30671</t>
+          <t>SAN DANIEL</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-11.580691</t>
+          <t>888</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-74.407473</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>-11.437829</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-74.490172</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>241306</t>
+          <t>242320</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30675</t>
+          <t>JORGE CHAVEZ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-11.6467</t>
+          <t>229</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-74.3715</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>-11.4236</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-74.48715</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>241801</t>
+          <t>242315</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SAN JUAN</t>
+          <t>COOPERATIVO PANGOA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-11.6477</t>
+          <t>272</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-74.3689</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>-11.435996</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-74.493294</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>242320</t>
+          <t>241801</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JORGE CHAVEZ</t>
+          <t>SAN JUAN</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-11.4236</t>
+          <t>285</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-74.48715</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>-11.6477</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-74.3689</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>756531</t>
+          <t>241306</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CIENTIFICA DEL VRAEM</t>
+          <t>30675</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-11.42922</t>
+          <t>253</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-74.49333</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>-11.6467</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-74.3715</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>241231</t>
+          <t>241269</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30636</t>
+          <t>30671</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-11.4334</t>
+          <t>256</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-74.4832</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>-11.580691</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-74.407473</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>242315</t>
+          <t>241245</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>COOPERATIVO PANGOA</t>
+          <t>30637 ANDRES AVELINO CACERES</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-11.435996</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-74.493294</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>-11.430946</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-74.487804</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>652958</t>
+          <t>241231</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SAN DANIEL</t>
+          <t>30636</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-11.437829</t>
+          <t>995</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-74.490172</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>-11.4334</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-74.4832</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>241245</t>
+          <t>241085</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>30637 ANDRES AVELINO CACERES</t>
+          <t>241</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-11.430946</t>
+          <t>263</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-74.487804</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>-11.4333</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-74.4853</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">

--- a/ZonasEscolares/excels/JUNIN-SATIPO-PANGOA.xlsx
+++ b/ZonasEscolares/excels/JUNIN-SATIPO-PANGOA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
